--- a/data/trans_dic/P36$otros-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36$otros-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, otros alimentos</t>
+          <t>Población que desayuna, otros alimentos (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,01</t>
+          <t>0,72; 2,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,11</t>
+          <t>0,21; 2,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,77</t>
+          <t>1,3; 4,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,34</t>
+          <t>0,39; 2,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,63</t>
+          <t>0,46; 2,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 7,36</t>
+          <t>3,11; 7,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,24</t>
+          <t>0,69; 2,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,92</t>
+          <t>0,46; 1,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,25</t>
+          <t>2,68; 5,47</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,28</t>
+          <t>0,61; 2,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,65</t>
+          <t>0,27; 1,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,05</t>
+          <t>2,73; 6,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,96</t>
+          <t>0,44; 2,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,06</t>
+          <t>0,85; 2,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,24</t>
+          <t>1,97; 5,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,73</t>
+          <t>0,68; 1,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,85</t>
+          <t>0,71; 2,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,06</t>
+          <t>2,65; 4,91</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,13</t>
+          <t>1,59; 4,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,83</t>
+          <t>0,56; 2,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,87</t>
+          <t>2,06; 5,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,69</t>
+          <t>0,28; 1,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,84</t>
+          <t>0,26; 1,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,83</t>
+          <t>2,08; 4,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,5</t>
+          <t>1,07; 2,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,72</t>
+          <t>0,58; 1,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,35</t>
+          <t>2,33; 4,4</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,05</t>
+          <t>0,63; 3,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,71</t>
+          <t>0,16; 1,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 7,73</t>
+          <t>3,82; 7,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,89</t>
+          <t>0,76; 2,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,11</t>
+          <t>0,68; 3,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 6,76</t>
+          <t>3,34; 6,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,45</t>
+          <t>0,93; 2,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,9</t>
+          <t>0,59; 1,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 6,54</t>
+          <t>4,01; 6,4</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,45</t>
+          <t>0,64; 3,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,84</t>
+          <t>0,22; 1,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 6,42</t>
+          <t>2,32; 6,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,03</t>
+          <t>0,53; 3,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,7</t>
+          <t>0,46; 2,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 6,36</t>
+          <t>2,48; 6,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,64</t>
+          <t>0,84; 2,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,78</t>
+          <t>0,45; 1,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,63</t>
+          <t>2,88; 5,75</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,59</t>
+          <t>0,96; 4,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,06</t>
+          <t>0,31; 2,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,43; 6,7</t>
+          <t>2,34; 6,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,5</t>
+          <t>2,5; 6,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,94</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,45</t>
+          <t>2,82; 7,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,98</t>
+          <t>2,09; 4,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,0</t>
+          <t>0,42; 1,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,06; 6,31</t>
+          <t>3,19; 6,17</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 5,5</t>
+          <t>0,63; 5,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 6,5</t>
+          <t>1,27; 7,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,99</t>
+          <t>2,23; 7,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,59</t>
+          <t>1,34; 5,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,62</t>
+          <t>0,0; 1,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,37; 7,19</t>
+          <t>2,62; 7,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,62</t>
+          <t>1,54; 4,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,36</t>
+          <t>0,67; 3,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,93; 6,37</t>
+          <t>2,88; 6,49</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,33</t>
+          <t>1,42; 2,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,55</t>
+          <t>0,76; 1,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,37; 4,77</t>
+          <t>3,35; 4,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,09</t>
+          <t>1,26; 2,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,54</t>
+          <t>0,82; 1,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,53; 4,84</t>
+          <t>3,51; 4,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,08</t>
+          <t>1,41; 2,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,38</t>
+          <t>0,86; 1,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,63; 4,61</t>
+          <t>3,62; 4,6</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, otros alimentos</t>
+          <t>Población que desayuna, otros alimentos (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3775; 14827</t>
+          <t>3533; 14509</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>949; 9599</t>
+          <t>957; 9666</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6265; 20008</t>
+          <t>5459; 20093</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1790; 10962</t>
+          <t>1834; 10750</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1984; 11242</t>
+          <t>1962; 11920</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12295; 29052</t>
+          <t>12266; 30249</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6660; 21546</t>
+          <t>6665; 20843</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4829; 16937</t>
+          <t>4025; 15870</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21298; 42763</t>
+          <t>21817; 44534</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4563; 16786</t>
+          <t>4502; 16549</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2043; 11333</t>
+          <t>1854; 11291</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16018; 35721</t>
+          <t>16091; 36006</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2726; 12238</t>
+          <t>2766; 12858</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5207; 18635</t>
+          <t>5153; 17888</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11627; 29523</t>
+          <t>11128; 28186</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8794; 23575</t>
+          <t>9233; 24724</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8751; 23898</t>
+          <t>9141; 25902</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31517; 58447</t>
+          <t>30609; 56613</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9574; 26197</t>
+          <t>10085; 28223</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4033; 19231</t>
+          <t>3779; 16427</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14174; 32589</t>
+          <t>13801; 33769</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2122; 11623</t>
+          <t>1960; 12590</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1813; 13033</t>
+          <t>1858; 12878</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13114; 31916</t>
+          <t>13765; 32167</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14407; 33143</t>
+          <t>14126; 32982</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8201; 23814</t>
+          <t>8053; 23878</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30855; 57830</t>
+          <t>31008; 58480</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3559; 15784</t>
+          <t>3242; 15548</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>980; 10494</t>
+          <t>982; 9346</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24922; 49793</t>
+          <t>24602; 47709</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3100; 14843</t>
+          <t>3895; 14970</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4256; 19170</t>
+          <t>4198; 18797</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20879; 43806</t>
+          <t>21673; 42539</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9073; 25277</t>
+          <t>9631; 26317</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6809; 23370</t>
+          <t>7203; 22624</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50791; 84501</t>
+          <t>51764; 82635</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2467; 13351</t>
+          <t>2463; 13189</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>939; 7894</t>
+          <t>929; 7800</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11715; 30662</t>
+          <t>11080; 30223</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2152; 12223</t>
+          <t>2156; 12920</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2075; 12085</t>
+          <t>2075; 12533</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11867; 31591</t>
+          <t>12301; 32640</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6772; 20892</t>
+          <t>6604; 20870</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4075; 15583</t>
+          <t>3971; 15877</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27241; 54836</t>
+          <t>28080; 56023</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2900; 13435</t>
+          <t>2822; 13345</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>994; 9484</t>
+          <t>962; 8646</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8124; 22411</t>
+          <t>7829; 22400</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8459; 22300</t>
+          <t>8572; 22641</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>887; 6883</t>
+          <t>0; 8222</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11162; 28135</t>
+          <t>10665; 28406</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14236; 31631</t>
+          <t>13271; 31072</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2783; 13277</t>
+          <t>2774; 12513</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21759; 44933</t>
+          <t>22725; 43954</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>955; 11552</t>
+          <t>1327; 12012</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2232; 16178</t>
+          <t>3171; 18213</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6298; 17839</t>
+          <t>5701; 18095</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5401; 18679</t>
+          <t>4470; 17849</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 6291</t>
+          <t>0; 7161</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9453; 28687</t>
+          <t>10440; 31220</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8527; 25101</t>
+          <t>8349; 25607</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4297; 21451</t>
+          <t>4283; 21970</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>19163; 41664</t>
+          <t>18829; 42465</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>46143; 76136</t>
+          <t>46331; 77733</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>24101; 52927</t>
+          <t>25950; 51016</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>114086; 161648</t>
+          <t>113648; 162985</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>41555; 70627</t>
+          <t>42427; 71113</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>29013; 54551</t>
+          <t>29090; 56910</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>125167; 171338</t>
+          <t>124407; 171662</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>96628; 138150</t>
+          <t>93955; 138486</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>61548; 96497</t>
+          <t>59747; 95957</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>251277; 319791</t>
+          <t>251000; 318902</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$otros-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36$otros-Edad-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,94</t>
+          <t>0,64; 3,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,13</t>
+          <t>0,21; 1,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,79</t>
+          <t>1,58; 5,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,3</t>
+          <t>0,39; 2,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,78</t>
+          <t>0,46; 2,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 7,66</t>
+          <t>3,11; 7,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,17</t>
+          <t>0,72; 2,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,8</t>
+          <t>0,54; 1,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 5,47</t>
+          <t>2,71; 5,33</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,25</t>
+          <t>0,6; 2,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,65</t>
+          <t>0,39; 1,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,1</t>
+          <t>2,61; 6,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,06</t>
+          <t>0,44; 2,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,94</t>
+          <t>0,75; 2,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,0</t>
+          <t>2,04; 5,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,82</t>
+          <t>0,7; 1,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,0</t>
+          <t>0,72; 1,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,91</t>
+          <t>2,68; 5,01</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,45</t>
+          <t>1,51; 4,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,42</t>
+          <t>0,58; 2,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,05</t>
+          <t>2,08; 4,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,83</t>
+          <t>0,27; 1,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,82</t>
+          <t>0,26; 2,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,86</t>
+          <t>1,99; 4,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,49</t>
+          <t>1,02; 2,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,72</t>
+          <t>0,56; 1,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,4</t>
+          <t>2,39; 4,38</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,01</t>
+          <t>0,61; 3,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,52</t>
+          <t>0,16; 1,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 7,41</t>
+          <t>3,63; 7,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,91</t>
+          <t>0,75; 2,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,05</t>
+          <t>0,67; 2,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,57</t>
+          <t>3,37; 6,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,55</t>
+          <t>0,88; 2,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,84</t>
+          <t>0,53; 1,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,01; 6,4</t>
+          <t>3,93; 6,62</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,41</t>
+          <t>0,61; 3,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,82</t>
+          <t>0,22; 1,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,32; 6,32</t>
+          <t>2,41; 6,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,2</t>
+          <t>0,59; 3,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,81</t>
+          <t>0,46; 2,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,57</t>
+          <t>2,52; 6,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,64</t>
+          <t>0,89; 2,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,81</t>
+          <t>0,45; 1,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,75</t>
+          <t>2,85; 5,71</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,56</t>
+          <t>0,97; 4,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,79</t>
+          <t>0,31; 2,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,34; 6,7</t>
+          <t>2,31; 6,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,5; 6,6</t>
+          <t>2,5; 6,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,25; 2,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,82; 7,52</t>
+          <t>2,83; 7,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,89</t>
+          <t>2,2; 4,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,89</t>
+          <t>0,44; 2,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,17</t>
+          <t>3,13; 6,1</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,72</t>
+          <t>0,78; 5,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 7,32</t>
+          <t>0,91; 7,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,09</t>
+          <t>2,19; 6,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,35</t>
+          <t>1,62; 5,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,62; 7,83</t>
+          <t>2,56; 7,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,71</t>
+          <t>1,44; 4,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,44</t>
+          <t>0,66; 3,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,49</t>
+          <t>2,83; 6,27</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,38</t>
+          <t>1,36; 2,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,49</t>
+          <t>0,74; 1,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,35; 4,81</t>
+          <t>3,38; 4,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,11</t>
+          <t>1,26; 2,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,6</t>
+          <t>0,82; 1,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,51; 4,85</t>
+          <t>3,56; 4,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,08</t>
+          <t>1,4; 2,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,38</t>
+          <t>0,88; 1,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,62; 4,6</t>
+          <t>3,59; 4,62</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3533; 14509</t>
+          <t>3180; 15149</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>957; 9666</t>
+          <t>945; 8676</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5459; 20093</t>
+          <t>6631; 21309</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1834; 10750</t>
+          <t>1817; 10828</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1962; 11920</t>
+          <t>1954; 11302</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12266; 30249</t>
+          <t>12265; 29089</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6665; 20843</t>
+          <t>6871; 20429</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4025; 15870</t>
+          <t>4790; 16916</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21817; 44534</t>
+          <t>22092; 43363</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4502; 16549</t>
+          <t>4433; 17158</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1854; 11291</t>
+          <t>2680; 12587</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16091; 36006</t>
+          <t>15416; 36622</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2766; 12858</t>
+          <t>2741; 13018</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5153; 17888</t>
+          <t>4579; 17100</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11128; 28186</t>
+          <t>11504; 28546</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9233; 24724</t>
+          <t>9457; 25054</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9141; 25902</t>
+          <t>9317; 24916</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30609; 56613</t>
+          <t>30925; 57790</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10085; 28223</t>
+          <t>9579; 26622</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3779; 16427</t>
+          <t>3955; 18270</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13801; 33769</t>
+          <t>13949; 33100</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1960; 12590</t>
+          <t>1871; 11243</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1858; 12878</t>
+          <t>1854; 14272</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13765; 32167</t>
+          <t>13170; 31635</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14126; 32982</t>
+          <t>13510; 31908</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8053; 23878</t>
+          <t>7708; 24859</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31008; 58480</t>
+          <t>31858; 58338</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3242; 15548</t>
+          <t>3141; 15534</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>982; 9346</t>
+          <t>982; 9626</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24602; 47709</t>
+          <t>23365; 47637</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3895; 14970</t>
+          <t>3864; 14969</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4198; 18797</t>
+          <t>4112; 17690</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21673; 42539</t>
+          <t>21808; 41834</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9631; 26317</t>
+          <t>9041; 26493</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7203; 22624</t>
+          <t>6459; 21763</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>51764; 82635</t>
+          <t>50796; 85537</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2463; 13189</t>
+          <t>2343; 13252</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>929; 7800</t>
+          <t>932; 7729</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11080; 30223</t>
+          <t>11531; 30920</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2156; 12920</t>
+          <t>2379; 14349</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2075; 12533</t>
+          <t>2044; 12276</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12301; 32640</t>
+          <t>12545; 33008</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6604; 20870</t>
+          <t>7007; 21067</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3971; 15877</t>
+          <t>3965; 15040</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28080; 56023</t>
+          <t>27785; 55683</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2822; 13345</t>
+          <t>2847; 12669</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>962; 8646</t>
+          <t>965; 9082</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7829; 22400</t>
+          <t>7715; 21648</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8572; 22641</t>
+          <t>8570; 22230</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 8222</t>
+          <t>891; 8317</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10665; 28406</t>
+          <t>10697; 27366</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13271; 31072</t>
+          <t>14011; 30356</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2774; 12513</t>
+          <t>2901; 13290</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22725; 43954</t>
+          <t>22312; 43403</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1327; 12012</t>
+          <t>1646; 12291</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3171; 18213</t>
+          <t>2264; 18795</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5701; 18095</t>
+          <t>5583; 16949</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4470; 17849</t>
+          <t>5414; 18750</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 7161</t>
+          <t>0; 7226</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10440; 31220</t>
+          <t>10223; 29056</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8349; 25607</t>
+          <t>7843; 24417</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4283; 21970</t>
+          <t>4236; 19562</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18829; 42465</t>
+          <t>18531; 41043</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>46331; 77733</t>
+          <t>44323; 76151</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>25950; 51016</t>
+          <t>25315; 50568</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>113648; 162985</t>
+          <t>114546; 164189</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>42427; 71113</t>
+          <t>42586; 71838</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>29090; 56910</t>
+          <t>29161; 54949</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>124407; 171662</t>
+          <t>126126; 175735</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>93955; 138486</t>
+          <t>93219; 136291</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>59747; 95957</t>
+          <t>61139; 95274</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>251000; 318902</t>
+          <t>248685; 320337</t>
         </is>
       </c>
     </row>
